--- a/healthcare_forms/011_health_assessment_template--healthcare_forms.xlsx
+++ b/healthcare_forms/011_health_assessment_template--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medications'}</t>
+          <t>medications</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medications'}</t>
+          <t>Medications</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'conditions'}</t>
+          <t>conditions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Conditions'}</t>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pain'}</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pain'}</t>
+          <t>Pain</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'nausea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Nausea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hypertension'}</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'epilepsy'}</t>
+          <t>epilepsy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Epilepsy'}</t>
+          <t>Epilepsy</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'cancer'}</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Cancer'}</t>
+          <t>Cancer</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'family_history'}</t>
+          <t>family_history</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Family History'}</t>
+          <t>Family History</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'family_history_2'}</t>
+          <t>family_history_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Family History 2'}</t>
+          <t>Family History 2</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'family_history_3'}</t>
+          <t>family_history_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Family History 3'}</t>
+          <t>Family History 3</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'family_history_4'}</t>
+          <t>family_history_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Family History 4'}</t>
+          <t>Family History 4</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'family_history_5'}</t>
+          <t>family_history_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Family History 5'}</t>
+          <t>Family History 5</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'medications'}</t>
+          <t>medications</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Medications'}</t>
+          <t>Medications</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medications_2'}</t>
+          <t>medications_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medications 2'}</t>
+          <t>Medications 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medications_3'}</t>
+          <t>medications_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medications 3'}</t>
+          <t>Medications 3</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'medications_4'}</t>
+          <t>medications_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Medications 4'}</t>
+          <t>Medications 4</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'medications_5'}</t>
+          <t>medications_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Medications 5'}</t>
+          <t>Medications 5</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'social_history'}</t>
+          <t>social_history</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Social History'}</t>
+          <t>Social History</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'social_history_2'}</t>
+          <t>social_history_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Social History 2'}</t>
+          <t>Social History 2</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'social_history_3'}</t>
+          <t>social_history_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Social History 3'}</t>
+          <t>Social History 3</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'social_history_4'}</t>
+          <t>social_history_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Social History 4'}</t>
+          <t>Social History 4</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'social_history_5'}</t>
+          <t>social_history_5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Social History 5'}</t>
+          <t>Social History 5</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'medical_test_1'}</t>
+          <t>medical_test_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Medical Test 1'}</t>
+          <t>Medical Test 1</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medical_test_2'}</t>
+          <t>medical_test_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medical Test 2'}</t>
+          <t>Medical Test 2</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medical_test_3'}</t>
+          <t>medical_test_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medical Test 3'}</t>
+          <t>Medical Test 3</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'medical_test_4'}</t>
+          <t>medical_test_4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Medical Test 4'}</t>
+          <t>Medical Test 4</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'medical_test_5'}</t>
+          <t>medical_test_5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Medical Test 5'}</t>
+          <t>Medical Test 5</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'medical_procedure_1'}</t>
+          <t>medical_procedure_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Medical Procedure 1'}</t>
+          <t>Medical Procedure 1</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medical_procedure_2'}</t>
+          <t>medical_procedure_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medical Procedure 2'}</t>
+          <t>Medical Procedure 2</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'medical_procedure_3'}</t>
+          <t>medical_procedure_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Medical Procedure 3'}</t>
+          <t>Medical Procedure 3</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'medical_procedure_4'}</t>
+          <t>medical_procedure_4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Medical Procedure 4'}</t>
+          <t>Medical Procedure 4</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'medical_procedure_5'}</t>
+          <t>medical_procedure_5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Medical Procedure 5'}</t>
+          <t>Medical Procedure 5</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'resuscitated'}</t>
+          <t>resuscitated</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Resuscitated'}</t>
+          <t>Resuscitated</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'discharged'}</t>
+          <t>discharged</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Discharged'}</t>
+          <t>Discharged</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'deceased'}</t>
+          <t>deceased</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Deceased'}</t>
+          <t>Deceased</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
